--- a/ig/test-tabs-svs/CodeSystem-TRE-R344-NiveauExpertise.xlsx
+++ b/ig/test-tabs-svs/CodeSystem-TRE-R344-NiveauExpertise.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="148">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,264 +118,267 @@
     <t>Count</t>
   </si>
   <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Uri</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>dateValid</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
+  </si>
+  <si>
+    <t>date de validité d'un code concept</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>dateMaj</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
+  </si>
+  <si>
+    <t>Date de mise à jour d'un code concept</t>
+  </si>
+  <si>
+    <t>dateFin</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
+  </si>
+  <si>
+    <t>Date de fin d'exploitation d'un code concept</t>
+  </si>
+  <si>
+    <t>deprecationDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
+  </si>
+  <si>
+    <t>Date Concept was deprecated</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>A property that indicates the status of the concept.</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>retirementDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
+  </si>
+  <si>
+    <t>Date Concept was retired</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Centre de référence labellisé</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Centre de compétences labellisé</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Structure spécialisée labellisée</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation des personnes en état de conscience altérée</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation des patients amputés, appareillés ou non</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation PREcoce Post-Aiguë Cardiologique (PREPAC)</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation PREcoce Post-Aiguë Respiratoire (PREPAR)</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation neuro-orthopédique</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation post-réanimation (SRPR)</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation PREcoce Post-Aiguë Neurologique (PREPAN)</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation des troubles des patients cérébro-lésés</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation des lésions médullaires</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation des obésités complexes</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation troubles cognitifs liés à une conduite addictive</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation du polyhandicap</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation des troubles du langage et des apprentissages</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Centre de recours pour chirurgie oncologique complexe</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Premier niveau de recours</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Deuxième niveau de recours</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Troisième niveau de recours</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Unité de réanimation pédiatrique de recours</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Filière endométriose - premier niveau de recours</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Filière endométriose - deuxième niveau de recours</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Filière endométriose - troisième niveau de recours</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Centre labellisé Covid-Long</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>Centre de réhabilitation psychosociale - Centre de recours labellisé</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>Centre de réhabilitation psychosociale - Centre de proximité labellisé</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>Unité neuro-vasculaire (UNV) de territoire</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Unité neuro-vasculaire (UNV) de recours</t>
+  </si>
+  <si>
     <t>39</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Uri</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>dateValid</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
-  </si>
-  <si>
-    <t>date de validité d'un code concept</t>
-  </si>
-  <si>
-    <t>dateTime</t>
-  </si>
-  <si>
-    <t>dateMaj</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
-  </si>
-  <si>
-    <t>Date de mise à jour d'un code concept</t>
-  </si>
-  <si>
-    <t>dateFin</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
-  </si>
-  <si>
-    <t>Date de fin d'exploitation d'un code concept</t>
-  </si>
-  <si>
-    <t>deprecationDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
-  </si>
-  <si>
-    <t>Date Concept was deprecated</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#status</t>
-  </si>
-  <si>
-    <t>A property that indicates the status of the concept.</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>retirementDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
-  </si>
-  <si>
-    <t>Date Concept was retired</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Centre de référence labellisé</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Centre de compétences labellisé</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Structure spécialisée labellisée</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation des personnes en état de conscience altérée</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation des patients amputés, appareillés ou non</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation PREcoce Post-Aiguë Cardiologique (PREPAC)</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation PREcoce Post-Aiguë Respiratoire (PREPAR)</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation neuro-orthopédique</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation post-réanimation (SRPR)</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation PREcoce Post-Aiguë Neurologique (PREPAN)</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation des troubles des patients cérébro-lésés</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation des lésions médullaires</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation des obésités complexes</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation troubles cognitifs liés à une conduite addictive</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation du polyhandicap</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation des troubles du langage et des apprentissages</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Centre de recours pour chirurgie oncologique complexe</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>Premier niveau de recours</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>Deuxième niveau de recours</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>Troisième niveau de recours</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>Unité de réanimation pédiatrique de recours</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>Filière endométriose - premier niveau de recours</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>Filière endométriose - deuxième niveau de recours</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>Filière endométriose - troisième niveau de recours</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>Centre labellisé Covid-Long</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>Centre de réhabilitation psychosociale - Centre de recours labellisé</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>Centre de réhabilitation psychosociale - Centre de proximité labellisé</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>Unité neuro-vasculaire (UNV) de territoire</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>Unité neuro-vasculaire (UNV) de recours</t>
-  </si>
-  <si>
     <t>Filière Obésité - Niveau 1 Conventionné Centres Spécialisés Obésité (CSO)</t>
   </si>
   <si>
@@ -400,9 +403,6 @@
     <t>Filière Obésité - Niveau 3 (Centre Spécialisé Obésité)</t>
   </si>
   <si>
-    <t>43</t>
-  </si>
-  <si>
     <t>Centre Ressources Autisme (CRA)</t>
   </si>
   <si>
@@ -427,13 +427,37 @@
     <t>47</t>
   </si>
   <si>
-    <t>Centre expert Parkinson</t>
+    <t>Centre expert maladie de Parkinson</t>
   </si>
   <si>
     <t>48</t>
   </si>
   <si>
     <t>Centre de ressources et de compétences sclérose en plaques (SEP)</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>Agrément Fédération Européenne des Services d'Urgence de la Main (FESUM) - SOS mains</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>Centre de Traitement des Brûlés (CTB)</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>Réseau France Santé</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>Autorisation par l’ARS pour la sous-traitance de préparation pharmaceutique</t>
   </si>
 </sst>
 </file>
@@ -849,7 +873,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1219,13 +1243,13 @@
         <v>61</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32">
@@ -1233,10 +1257,10 @@
         <v>61</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D32" s="2"/>
     </row>
@@ -1245,10 +1269,10 @@
         <v>61</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D33" s="2"/>
     </row>
@@ -1257,10 +1281,10 @@
         <v>61</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D34" s="2"/>
     </row>
@@ -1269,7 +1293,7 @@
         <v>61</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>128</v>
+        <v>34</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>129</v>
@@ -1335,6 +1359,54 @@
         <v>139</v>
       </c>
       <c r="D40" s="2"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="D41" s="2"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="D42" s="2"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="D43" s="2"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="D44" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
